--- a/Ready_models/hf_aft_covariance_matrix.xlsx
+++ b/Ready_models/hf_aft_covariance_matrix.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mu_</t>
+          <t>lambda_</t>
         </is>
       </c>
       <c r="D1" s="1" t="n"/>
@@ -496,7 +496,7 @@
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>sigma_</t>
+          <t>rho_</t>
         </is>
       </c>
     </row>
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>creatinine_phosphokinase</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>ejection_fraction</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>high_blood_pressure</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>serum_creatinine</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>serum_sodium</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>mu_</t>
+          <t>lambda_</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -571,28 +571,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0001086341630740417</v>
+        <v>9.153536735349408e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>-8.880800425696633e-05</v>
+        <v>-5.752351504214755e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.151015208423618e-05</v>
+        <v>3.401679981330528e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0001230326496393185</v>
+        <v>-1.464530343009398e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.829509929846434e-05</v>
+        <v>4.938822627763245e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.163200808992373e-06</v>
+        <v>-5.948672508069698e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005848052569250611</v>
+        <v>-0.005660681327890592</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0001813485600090365</v>
+        <v>0.0002397251526104773</v>
       </c>
     </row>
     <row r="5">
@@ -603,156 +603,156 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-8.880800425696984e-05</v>
+        <v>-5.752351504214775e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06092716417455001</v>
+        <v>0.04853596302758818</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0001567454367832023</v>
+        <v>4.277414006513624e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001122782546202144</v>
+        <v>-0.0002575981657267323</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0008130119329922275</v>
+        <v>-0.003611149891926</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0003667436756752862</v>
+        <v>-0.0007156171801679776</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03359397816325845</v>
+        <v>-0.01192779055844354</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0009727092101384145</v>
+        <v>0.001297763134821071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>ejection_fraction</t>
+          <t>creatinine_phosphokinase</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2.151015208423606e-05</v>
+        <v>3.401679981330526e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0001567454367832058</v>
+        <v>4.277414006513624e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000127909181958888</v>
+        <v>1.065118156974056e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.111071382365469e-06</v>
+        <v>-9.707181501035082e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001732356959035743</v>
+        <v>9.990869741856138e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.806267791403167e-05</v>
+        <v>8.642297836944906e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003945949259376798</v>
+        <v>-1.08673576845847e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002318380270477823</v>
+        <v>9.718234966108552e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>high_blood_pressure</t>
+          <t>ejection_fraction</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.00012303264963932</v>
+        <v>-1.464530343009395e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001122782546202145</v>
+        <v>-0.0002575981657267322</v>
       </c>
       <c r="E7" t="n">
-        <v>4.111071382367996e-06</v>
+        <v>-9.707181501035072e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06419768742004608</v>
+        <v>0.000125301689624766</v>
       </c>
       <c r="G7" t="n">
-        <v>8.967678952348538e-05</v>
+        <v>-5.579480445058845e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0002618517614221416</v>
+        <v>-0.0001462172231899993</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01816623463728887</v>
+        <v>-0.002511807306009317</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.00109765125453563</v>
+        <v>-0.0003348744256015277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>serum_creatinine</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-4.829509929846521e-05</v>
+        <v>4.938822627763444e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0008130119329921909</v>
+        <v>-0.003611149891926003</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.000173235695903573</v>
+        <v>9.990869741856161e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>8.967678952352272e-05</v>
+        <v>-5.579480445058807e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01099654903566454</v>
+        <v>0.04838419937856671</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004532786326772635</v>
+        <v>-0.001268769486543471</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07138687051667138</v>
+        <v>-0.01875507226498481</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.00169916578769135</v>
+        <v>0.00153805433065034</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>serum_sodium</t>
+          <t>serum_creatinine</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2.163200808992068e-06</v>
+        <v>-5.94867250806982e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0003667436756752449</v>
+        <v>-0.0007156171801679773</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.806267791403134e-05</v>
+        <v>8.642297836944903e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0002618517614221008</v>
+        <v>-0.0001462172231899994</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004532786326772915</v>
+        <v>-0.001268769486543473</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0007193886117810508</v>
+        <v>0.004719357956183839</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09620459435724908</v>
+        <v>-0.004405478304426278</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001916991152204358</v>
+        <v>0.001764192856255264</v>
       </c>
     </row>
     <row r="10">
@@ -763,34 +763,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.005848052569250631</v>
+        <v>-0.005660681327890591</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03359397816325261</v>
+        <v>-0.01192779055844355</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003945949259376749</v>
+        <v>-1.08673576845847e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01816623463728325</v>
+        <v>-0.002511807306009313</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07138687051667512</v>
+        <v>-0.01875507226498465</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09620459435724892</v>
+        <v>-0.004405478304426293</v>
       </c>
       <c r="I10" t="n">
-        <v>13.40386215144543</v>
+        <v>0.5046042876173604</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.01154642759982059</v>
+        <v>-0.01538925901138056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>sigma_</t>
+          <t>rho_</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -799,28 +799,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.0001813485600090351</v>
+        <v>0.0002397251526104766</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0009727092101384177</v>
+        <v>0.001297763134821069</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002318380270477818</v>
+        <v>9.718234966108535e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.001097651254535629</v>
+        <v>-0.0003348744256015279</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.001699165787691333</v>
+        <v>0.001538054330650332</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0001916991152204524</v>
+        <v>0.001764192856255263</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01154642759982294</v>
+        <v>-0.0153892590113805</v>
       </c>
       <c r="J11" t="n">
-        <v>0.006430212963632384</v>
+        <v>0.007893160637686593</v>
       </c>
     </row>
   </sheetData>
